--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101342</v>
+        <v>101346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>98002</v>
+        <v>98006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>101342</v>
+        <v>101346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101342</v>
+        <v>101346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101346</v>
+        <v>101348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133872035</v>
+        <v>133872034</v>
       </c>
       <c r="B3" t="n">
-        <v>98006</v>
+        <v>101348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>601904</v>
       </c>
       <c r="R3" t="n">
-        <v>6654991</v>
+        <v>6655008</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133872034</v>
+        <v>133872035</v>
       </c>
       <c r="B4" t="n">
-        <v>101346</v>
+        <v>98008</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601904</v>
+        <v>602006</v>
       </c>
       <c r="R4" t="n">
-        <v>6655008</v>
+        <v>6654991</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101346</v>
+        <v>101348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133872034</v>
+        <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>101348</v>
+        <v>98036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601904</v>
+        <v>602006</v>
       </c>
       <c r="R3" t="n">
-        <v>6655008</v>
+        <v>6654991</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133872035</v>
+        <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>98008</v>
+        <v>101376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602006</v>
+        <v>601904</v>
       </c>
       <c r="R4" t="n">
-        <v>6654991</v>
+        <v>6655008</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>98036</v>
+        <v>98046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101388</v>
+        <v>101389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>98048</v>
+        <v>98049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>101388</v>
+        <v>101389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101388</v>
+        <v>101389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133872036</v>
       </c>
       <c r="B2" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133872035</v>
       </c>
       <c r="B3" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133872034</v>
       </c>
       <c r="B4" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133872030</v>
       </c>
       <c r="B5" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133872036</v>
+        <v>133872027</v>
       </c>
       <c r="B2" t="n">
-        <v>101396</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602006</v>
+        <v>602083</v>
       </c>
       <c r="R2" t="n">
-        <v>6654991</v>
+        <v>6654984</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133872035</v>
+        <v>133872031</v>
       </c>
       <c r="B3" t="n">
-        <v>98056</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602006</v>
+        <v>601883</v>
       </c>
       <c r="R3" t="n">
-        <v>6654991</v>
+        <v>6655007</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,48 +889,65 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133872034</v>
+        <v>94565026</v>
       </c>
       <c r="B4" t="n">
-        <v>101396</v>
+        <v>45049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Runhällen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601904</v>
+        <v>602189</v>
       </c>
       <c r="R4" t="n">
-        <v>6655008</v>
+        <v>6655017</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,28 +985,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Samuel Persson, Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133872030</v>
+        <v>133872040</v>
       </c>
       <c r="B5" t="n">
-        <v>101396</v>
+        <v>98219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1015,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219815</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Runhällen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601901</v>
+        <v>602120</v>
       </c>
       <c r="R5" t="n">
-        <v>6654995</v>
+        <v>6654991</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,27 +1076,18 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:47</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1100,6 +1103,541 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133872035</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602006</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6654991</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133872030</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>601901</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6654995</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133872034</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>601904</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6655008</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133872036</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6654991</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133872033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Runhällen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>601898</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6654983</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21712-2026 artfynd.xlsx
+++ b/artfynd/A 21712-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872027</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94565026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872040</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872035</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872030</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872034</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872036</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,8 +1683,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133872033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>